--- a/02.FOMD/03.extraction/02.09_FOMD_extraction/MC/JA_Mideg_06_Maize_In/Fig2_3_JA_Mideg_06_Maize_In.xlsx
+++ b/02.FOMD/03.extraction/02.09_FOMD_extraction/MC/JA_Mideg_06_Maize_In/Fig2_3_JA_Mideg_06_Maize_In.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Otros ordenadores\Mi portátil\Mario\Trabajo\Trabajo_Alliance\3_Projects\LOCAL_MC_AE Evidence Hub\0909\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/03.extraction/02.09_FOMD_extraction/MC/JA_Mideg_06_Maize_In/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743CD5FC-75A7-4E50-93E5-A416086DF5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="13_ncr:1_{743CD5FC-75A7-4E50-93E5-A416086DF5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98785BA4-AFCF-4200-A8AA-D33BCDD8167E}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-2130" windowWidth="38640" windowHeight="21120" xr2:uid="{71A907CE-EFB4-45DB-A88C-C458D4A65B28}"/>
+    <workbookView xWindow="-19305" yWindow="-2010" windowWidth="19410" windowHeight="20985" xr2:uid="{71A907CE-EFB4-45DB-A88C-C458D4A65B28}"/>
   </bookViews>
   <sheets>
-    <sheet name="Fig. 2" sheetId="1" r:id="rId1"/>
-    <sheet name="Fig. 3" sheetId="2" r:id="rId2"/>
+    <sheet name="Fig. 1" sheetId="3" r:id="rId1"/>
+    <sheet name="Fig. 2" sheetId="1" r:id="rId2"/>
+    <sheet name="Fig. 3" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="22">
   <si>
     <t xml:space="preserve"> Upper</t>
   </si>
@@ -85,13 +86,37 @@
   </si>
   <si>
     <t>Upper/Mean</t>
+  </si>
+  <si>
+    <t>B. Fusca</t>
+  </si>
+  <si>
+    <t>Egg batch number</t>
+  </si>
+  <si>
+    <t>C. partellas</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>Claude Values</t>
+  </si>
+  <si>
+    <t>Deltas Claude - Digitizer</t>
+  </si>
+  <si>
+    <t>Deltas % (relative to Digitizer)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,8 +124,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -143,6 +176,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -156,12 +201,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -170,18 +224,17 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -200,6 +253,61 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>149225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>19413</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>280</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C219527E-A5A6-E85D-122C-66EEFBF18F03}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2368550" y="2863850"/>
+          <a:ext cx="7061563" cy="5461280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -248,7 +356,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -612,124 +720,613 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="7">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{55501148-AF5E-4116-BC76-6CBC53617DE4}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;1344a67d-4c6c-4ccb-9589-b12f369c2fa5&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D75A9FD8-FFBE-45EC-90E0-1EE86DF9F59C}">
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="21.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="2"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B4">
+        <v>18.589211618257199</v>
+      </c>
+      <c r="C4">
+        <v>14.6058091286307</v>
+      </c>
+      <c r="D4">
+        <v>37.178423236514497</v>
+      </c>
+      <c r="E4">
+        <v>32.199170124481299</v>
+      </c>
+      <c r="F4">
+        <v>26.5560165975103</v>
+      </c>
+      <c r="G4">
+        <v>23.734439834024901</v>
+      </c>
+      <c r="H4">
+        <v>62.240663900414901</v>
+      </c>
+      <c r="I4">
+        <v>44.481327800829803</v>
+      </c>
+      <c r="J4">
+        <v>14.582278481012599</v>
+      </c>
+      <c r="K4">
+        <v>12.9113924050632</v>
+      </c>
+      <c r="L4">
+        <v>58.177215189873401</v>
+      </c>
+      <c r="M4">
+        <v>43.443037974683499</v>
+      </c>
+      <c r="N4">
+        <v>21.1139240506329</v>
+      </c>
+      <c r="O4">
+        <v>14.734177215189799</v>
+      </c>
+      <c r="P4">
+        <v>54.835443037974599</v>
+      </c>
+      <c r="Q4">
+        <v>49.8227848101265</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" t="s">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <f>B4-C4</f>
+        <v>3.9834024896264992</v>
+      </c>
+      <c r="D6">
+        <f>D4-E4</f>
+        <v>4.9792531120331986</v>
+      </c>
+      <c r="F6">
+        <f>F4-G4</f>
+        <v>2.8215767634853997</v>
+      </c>
+      <c r="H6">
+        <f>H4-I4</f>
+        <v>17.759336099585099</v>
+      </c>
+      <c r="J6">
+        <f>J4-K4</f>
+        <v>1.6708860759493991</v>
+      </c>
+      <c r="L6">
+        <f>L4-M4</f>
+        <v>14.734177215189902</v>
+      </c>
+      <c r="N6">
+        <f>N4-O4</f>
+        <v>6.3797468354431004</v>
+      </c>
+      <c r="P6">
+        <f>P4-Q4</f>
+        <v>5.0126582278480996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="10">
+        <v>14.2</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10">
+        <v>31.7</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10">
+        <v>23.2</v>
+      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10">
+        <v>43.7</v>
+      </c>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10">
+        <v>12.3</v>
+      </c>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10">
+        <v>42.8</v>
+      </c>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10">
+        <v>14.3</v>
+      </c>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B8" s="11"/>
+      <c r="C8" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10">
+        <v>5.4</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10">
+        <v>18</v>
+      </c>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10">
+        <v>15.1</v>
+      </c>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10">
+        <v>6.7</v>
+      </c>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <f>C7-C4</f>
+        <v>-0.4058091286307004</v>
+      </c>
+      <c r="E10">
+        <f>E7-E4</f>
+        <v>-0.49917012448129938</v>
+      </c>
+      <c r="G10">
+        <f>G7-G4</f>
+        <v>-0.53443983402490147</v>
+      </c>
+      <c r="I10">
+        <f>I7-I4</f>
+        <v>-0.78132780082979991</v>
+      </c>
+      <c r="K10">
+        <f>K7-K4</f>
+        <v>-0.61139240506319936</v>
+      </c>
+      <c r="M10">
+        <f>M7-M4</f>
+        <v>-0.64303797468350155</v>
+      </c>
+      <c r="O10">
+        <f>O7-O4</f>
+        <v>-0.43417721518979846</v>
+      </c>
+      <c r="Q10">
+        <f>Q7-Q4</f>
+        <v>-0.42278481012650104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <f>C8-B6</f>
+        <v>0.41659751037350112</v>
+      </c>
+      <c r="E11">
+        <f>E8-D6</f>
+        <v>0.42074688796680171</v>
+      </c>
+      <c r="G11">
+        <f>G8-F6</f>
+        <v>0.47842323651460017</v>
+      </c>
+      <c r="I11">
+        <f>I8-H6</f>
+        <v>0.24066390041490138</v>
+      </c>
+      <c r="K11">
+        <f>K8-J6</f>
+        <v>0.82911392405060091</v>
+      </c>
+      <c r="M11">
+        <f>M8-L6</f>
+        <v>0.36582278481009745</v>
+      </c>
+      <c r="O11">
+        <f>O8-N6</f>
+        <v>0.32025316455689978</v>
+      </c>
+      <c r="Q11">
+        <f>Q8-P6</f>
+        <v>0.18734177215190062</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="12">
+        <f>C10/C4</f>
+        <v>-2.7784090909090578E-2</v>
+      </c>
+      <c r="E13" s="12">
+        <f>E10/E4</f>
+        <v>-1.550257731958676E-2</v>
+      </c>
+      <c r="G13" s="12">
+        <f>G10/G4</f>
+        <v>-2.2517482517482732E-2</v>
+      </c>
+      <c r="I13" s="12">
+        <f>I10/I4</f>
+        <v>-1.7565298507461014E-2</v>
+      </c>
+      <c r="K13" s="12">
+        <f>K10/K4</f>
+        <v>-4.7352941176463811E-2</v>
+      </c>
+      <c r="M13" s="12">
+        <f>M10/M4</f>
+        <v>-1.4801864801863834E-2</v>
+      </c>
+      <c r="O13" s="12">
+        <f>O10/O4</f>
+        <v>-2.9467353951885097E-2</v>
+      </c>
+      <c r="Q13" s="12">
+        <f>Q10/Q4</f>
+        <v>-8.4857723577219605E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A14" s="9"/>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="12">
+        <f>C11/B6</f>
+        <v>0.10458333333334917</v>
+      </c>
+      <c r="E14" s="12">
+        <f>E11/D6</f>
+        <v>8.4499999999999284E-2</v>
+      </c>
+      <c r="G14" s="12">
+        <f>G11/F6</f>
+        <v>0.16955882352944385</v>
+      </c>
+      <c r="I14" s="12">
+        <f>I11/H6</f>
+        <v>1.3551401869156801E-2</v>
+      </c>
+      <c r="K14" s="12">
+        <f>K11/J6</f>
+        <v>0.49621212121209257</v>
+      </c>
+      <c r="M14" s="12">
+        <f>M11/L6</f>
+        <v>2.4828178694156048E-2</v>
+      </c>
+      <c r="O14" s="12">
+        <f>O11/N6</f>
+        <v>5.0198412698402452E-2</v>
+      </c>
+      <c r="Q14" s="12">
+        <f>Q11/P6</f>
+        <v>3.737373737373776E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="B1:Q1"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="J2:Q2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C1A548-32E0-4627-9D60-5A8A351A2673}">
   <dimension ref="A1:Y6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="8" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="5" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="6" t="s">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="5" t="s">
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5" t="s">
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5" t="s">
+      <c r="K3" s="2"/>
+      <c r="L3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="6" t="s">
+      <c r="M3" s="2"/>
+      <c r="N3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6" t="s">
+      <c r="O3" s="5"/>
+      <c r="P3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6" t="s">
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="S3" s="6"/>
-      <c r="T3" s="5" t="s">
+      <c r="S3" s="5"/>
+      <c r="T3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5" t="s">
+      <c r="U3" s="2"/>
+      <c r="V3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5" t="s">
+      <c r="W3" s="2"/>
+      <c r="X3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="Y3" s="5"/>
+      <c r="Y3" s="2"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B4">
@@ -934,6 +1531,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="T3:U3"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="N1:Y1"/>
@@ -950,15 +1549,13 @@
     <mergeCell ref="X3:Y3"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="T3:U3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86424184-4EAD-4DA6-957C-2EBC20D3581D}">
   <dimension ref="A1:Y4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -967,86 +1564,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="2" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="4" t="s">
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="6"/>
+      <c r="H2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
+      <c r="I2" s="6"/>
+      <c r="J2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
+      <c r="K2" s="6"/>
+      <c r="L2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3" t="s">
+      <c r="M2" s="6"/>
+      <c r="N2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3" t="s">
+      <c r="O2" s="6"/>
+      <c r="P2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3" t="s">
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3" t="s">
+      <c r="S2" s="6"/>
+      <c r="T2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3" t="s">
+      <c r="U2" s="6"/>
+      <c r="V2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3" t="s">
+      <c r="W2" s="6"/>
+      <c r="X2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="Y2" s="3"/>
+      <c r="Y2" s="6"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -1180,21 +1777,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R1:Y1"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:Y2"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="R1:Y1"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="J1:Q1"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1202,6 +1799,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -1402,34 +2019,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBDDB07F-F52B-4150-ADC6-01181D3F46CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15075237-7FDE-405B-9832-02BED393E3AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B60A5163-02E6-48E7-AC55-ED4847AD60F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B60A5163-02E6-48E7-AC55-ED4847AD60F0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15075237-7FDE-405B-9832-02BED393E3AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBDDB07F-F52B-4150-ADC6-01181D3F46CF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>